--- a/healthcare_forms/028_health_insurance_plan_assessment_form--healthcare_forms.xlsx
+++ b/healthcare_forms/028_health_insurance_plan_assessment_form--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="39" customWidth="1" min="2" max="2"/>
-    <col width="39" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'individual'}</t>
+          <t>individual</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Individual'}</t>
+          <t>Individual</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'family'}</t>
+          <t>family</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Family'}</t>
+          <t>Family</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'group'}</t>
+          <t>group</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Group'}</t>
+          <t>Group</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'health_insurance'}</t>
+          <t>health_insurance</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Health Insurance'}</t>
+          <t>Health Insurance</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'prescription'}</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Prescription'}</t>
+          <t>Prescription</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'local'}</t>
+          <t>local</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Local'}</t>
+          <t>Local</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'nationwide'}</t>
+          <t>nationwide</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Nationwide'}</t>
+          <t>Nationwide</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'regional'}</t>
+          <t>regional</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Regional'}</t>
+          <t>Regional</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'cancelled'}</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Cancelled'}</t>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'expired'}</t>
+          <t>expired</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Expired'}</t>
+          <t>Expired</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'individual'}</t>
+          <t>individual</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Individual'}</t>
+          <t>Individual</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'group'}</t>
+          <t>group</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Group'}</t>
+          <t>Group</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'family'}</t>
+          <t>family</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Family'}</t>
+          <t>Family</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'quarterly'}</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Quarterly'}</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'annually'}</t>
+          <t>annually</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Annually'}</t>
+          <t>Annually</t>
         </is>
       </c>
     </row>
